--- a/data/trans_camb/P19C03-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P19C03-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-26,07; -9,11</t>
+          <t>-25,99; -9,09</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-17,5; 0,06</t>
+          <t>-18,01; 0,17</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-28,92; -13,7</t>
+          <t>-29,13; -12,61</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-23,22; -5,03</t>
+          <t>-24,05; -6,27</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-27,94; -10,53</t>
+          <t>-27,78; -9,82</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-26,67; -9,56</t>
+          <t>-26,57; -9,46</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-22,3; -9,89</t>
+          <t>-22,14; -9,85</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-20,34; -7,43</t>
+          <t>-20,07; -6,88</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-25,7; -14,01</t>
+          <t>-25,81; -13,67</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-63,08; -29,23</t>
+          <t>-62,74; -27,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-43,13; 1,04</t>
+          <t>-42,75; 1,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-72,08; -43,64</t>
+          <t>-72,44; -41,77</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-51,01; -13,59</t>
+          <t>-52,2; -17,35</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-59,51; -28,24</t>
+          <t>-59,25; -27,66</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-57,35; -26,3</t>
+          <t>-57,18; -27,16</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-53,27; -28,25</t>
+          <t>-52,75; -28,22</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-47,87; -21,45</t>
+          <t>-47,35; -19,84</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-61,44; -39,98</t>
+          <t>-61,2; -39,34</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,3; 3,03</t>
+          <t>-9,76; 3,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,46; 6,63</t>
+          <t>-8,41; 5,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-13,24; 0,47</t>
+          <t>-12,91; 1,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,17; 6,38</t>
+          <t>-6,07; 6,03</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-10,62; 2,01</t>
+          <t>-9,86; 2,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-14,27; -3,23</t>
+          <t>-14,25; -3,21</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-6,37; 2,9</t>
+          <t>-5,89; 2,98</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-7,01; 1,87</t>
+          <t>-7,32; 2,03</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-12,03; -2,7</t>
+          <t>-12,11; -3,06</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-27,71; 10,18</t>
+          <t>-26,46; 11,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-19,96; 21,83</t>
+          <t>-22,98; 19,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-35,46; 1,87</t>
+          <t>-34,69; 6,06</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-18,5; 22,74</t>
+          <t>-18,06; 21,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-31,88; 7,31</t>
+          <t>-29,92; 8,5</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-41,25; -11,6</t>
+          <t>-41,57; -11,1</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-18,72; 9,41</t>
+          <t>-17,25; 9,82</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-20,41; 6,21</t>
+          <t>-21,32; 6,84</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-35,17; -9,23</t>
+          <t>-35,29; -10,04</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,06; 9,54</t>
+          <t>-7,77; 9,32</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-11,44; 3,6</t>
+          <t>-12,65; 3,73</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-20,32; -5,67</t>
+          <t>-21,11; -5,94</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-10,59; 4,02</t>
+          <t>-10,2; 5,1</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-12,93; 1,2</t>
+          <t>-12,26; 1,95</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-22,38; -9,95</t>
+          <t>-21,05; -9,19</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-6,32; 4,67</t>
+          <t>-6,58; 4,27</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-9,82; 1,16</t>
+          <t>-10,06; 0,95</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-19,35; -9,35</t>
+          <t>-19,52; -10,08</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-19,59; 36,2</t>
+          <t>-21,13; 34,71</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-31,68; 13,81</t>
+          <t>-35,56; 13,63</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-58,33; -20,99</t>
+          <t>-58,39; -22,2</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-31,42; 15,68</t>
+          <t>-30,06; 20,53</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-37,75; 5,27</t>
+          <t>-37,92; 6,69</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-65,14; -38,38</t>
+          <t>-63,58; -35,76</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-18,39; 17,34</t>
+          <t>-20,02; 15,32</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-29,43; 4,48</t>
+          <t>-29,61; 3,93</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-57,67; -34,23</t>
+          <t>-57,93; -36,18</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,74; 10,13</t>
+          <t>-5,17; 10,01</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-20,47; -5,64</t>
+          <t>-20,33; -6,29</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-20,61; -2,62</t>
+          <t>-19,85; -3,34</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-13,14; 0,28</t>
+          <t>-14,17; 0,35</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-14,86; -0,25</t>
+          <t>-14,17; -0,54</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-19,8; 8,82</t>
+          <t>-20,38; 7,05</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-7,48; 2,99</t>
+          <t>-7,84; 2,42</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-14,75; -5,24</t>
+          <t>-15,51; -5,73</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-17,77; -0,58</t>
+          <t>-17,93; 0,23</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-16,46; 36,96</t>
+          <t>-14,85; 35,53</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-57,81; -20,87</t>
+          <t>-57,41; -22,88</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-58,36; -7,32</t>
+          <t>-57,65; -10,5</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-37,81; 1,83</t>
+          <t>-40,59; 1,22</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-41,58; -0,48</t>
+          <t>-41,2; -1,92</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-59,83; 29,73</t>
+          <t>-60,91; 27,03</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-21,64; 10,92</t>
+          <t>-23,11; 8,05</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-44,0; -18,9</t>
+          <t>-44,72; -19,41</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-54,87; -2,1</t>
+          <t>-54,34; 1,08</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,63; 12,84</t>
+          <t>-7,33; 12,25</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-14,22; 6,71</t>
+          <t>-14,7; 5,63</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-15,73; 1,09</t>
+          <t>-16,38; 1,06</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-6,87; 11,95</t>
+          <t>-8,46; 10,85</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-12,66; 7,45</t>
+          <t>-12,56; 6,41</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-14,52; 2,36</t>
+          <t>-13,56; 2,93</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 8,53</t>
+          <t>-4,39; 9,24</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-11,0; 2,82</t>
+          <t>-11,75; 2,05</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-12,14; 0,14</t>
+          <t>-12,13; -0,7</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-20,77; 51,49</t>
+          <t>-22,55; 48,83</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-44,12; 26,88</t>
+          <t>-45,0; 23,37</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-47,6; 4,69</t>
+          <t>-47,91; 4,57</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-22,06; 51,24</t>
+          <t>-25,34; 46,57</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-39,87; 32,93</t>
+          <t>-38,43; 27,22</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-41,34; 10,79</t>
+          <t>-39,24; 14,15</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-14,89; 34,4</t>
+          <t>-14,33; 39,03</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-35,05; 10,82</t>
+          <t>-36,96; 8,47</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-37,6; 1,24</t>
+          <t>-37,44; -3,05</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-10,81; 5,23</t>
+          <t>-11,34; 6,61</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-15,11; 1,84</t>
+          <t>-15,21; 1,83</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-14,04; 2,55</t>
+          <t>-14,22; 2,08</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-7,71; 8,35</t>
+          <t>-7,69; 8,64</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-12,93; 3,45</t>
+          <t>-12,35; 3,89</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-16,64; -2,43</t>
+          <t>-17,86; -3,23</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-6,22; 5,08</t>
+          <t>-6,7; 4,43</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-11,14; 0,06</t>
+          <t>-10,98; 0,5</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-12,93; -2,59</t>
+          <t>-12,66; -2,05</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-33,73; 21,34</t>
+          <t>-34,19; 28,28</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-44,36; 8,34</t>
+          <t>-45,15; 7,49</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-40,97; 11,15</t>
+          <t>-42,42; 8,28</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-24,59; 37,95</t>
+          <t>-24,52; 39,79</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-41,9; 16,8</t>
+          <t>-40,52; 18,99</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-54,44; -9,97</t>
+          <t>-56,88; -14,13</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-20,05; 21,15</t>
+          <t>-21,95; 17,93</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-37,54; -0,16</t>
+          <t>-36,26; 2,47</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-43,32; -10,79</t>
+          <t>-41,55; -7,98</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-9,64; 2,42</t>
+          <t>-8,39; 2,45</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 8,42</t>
+          <t>-4,89; 9,04</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-15,97; -4,34</t>
+          <t>-16,52; -3,95</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-8,96; 1,89</t>
+          <t>-8,7; 2,86</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 7,76</t>
+          <t>-3,98; 7,76</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-26,22; -8,83</t>
+          <t>-24,94; -8,97</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-7,47; 0,91</t>
+          <t>-7,4; 0,82</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 6,81</t>
+          <t>-2,34; 6,65</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-22,49; -8,68</t>
+          <t>-21,2; -8,73</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-26,41; 8,38</t>
+          <t>-23,0; 8,09</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-12,32; 28,29</t>
+          <t>-13,19; 30,27</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-44,26; -14,51</t>
+          <t>-44,97; -13,19</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-27,11; 6,39</t>
+          <t>-26,0; 9,78</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-12,2; 27,44</t>
+          <t>-12,03; 27,1</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-78,12; -28,76</t>
+          <t>-77,01; -29,27</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-21,89; 2,87</t>
+          <t>-21,68; 2,82</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-6,2; 22,86</t>
+          <t>-7,0; 22,33</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-67,01; -28,33</t>
+          <t>-62,85; -28,04</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 6,93</t>
+          <t>-4,16; 6,67</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-9,88; 1,1</t>
+          <t>-9,95; 0,55</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-31,04; -18,01</t>
+          <t>-30,26; -18,16</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-6,97; 4,05</t>
+          <t>-7,49; 3,99</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-12,82; -2,27</t>
+          <t>-13,09; -2,34</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-27,38; -18,57</t>
+          <t>-27,72; -18,68</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 3,22</t>
+          <t>-4,03; 3,46</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-10,31; -2,8</t>
+          <t>-10,5; -2,94</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-28,47; -19,93</t>
+          <t>-28,61; -20,04</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-11,61; 25,04</t>
+          <t>-11,87; 23,84</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-28,94; 4,21</t>
+          <t>-29,29; 1,95</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-89,21; -62,22</t>
+          <t>-88,33; -62,7</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-18,28; 12,66</t>
+          <t>-19,17; 12,47</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-34,05; -7,12</t>
+          <t>-34,53; -7,09</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-71,59; -57,93</t>
+          <t>-71,91; -58,12</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-12,52; 10,28</t>
+          <t>-11,93; 11,18</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-29,07; -8,86</t>
+          <t>-29,46; -9,31</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-83,68; -63,78</t>
+          <t>-82,41; -63,87</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 0,59</t>
+          <t>-4,59; 0,43</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-6,93; -1,73</t>
+          <t>-6,92; -1,84</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-18,39; -11,29</t>
+          <t>-18,41; -11,35</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-5,67; -0,84</t>
+          <t>-5,43; -0,57</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-8,03; -3,15</t>
+          <t>-8,11; -3,24</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-18,2; -11,53</t>
+          <t>-18,25; -11,76</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-4,39; -0,76</t>
+          <t>-4,53; -0,98</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-7,08; -3,45</t>
+          <t>-6,89; -3,27</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-16,97; -12,26</t>
+          <t>-16,68; -12,24</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-14,02; 1,98</t>
+          <t>-13,73; 1,46</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-21,12; -5,98</t>
+          <t>-20,69; -5,48</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-56,54; -36,05</t>
+          <t>-57,45; -36,86</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-17,08; -2,93</t>
+          <t>-16,3; -1,89</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-24,13; -10,36</t>
+          <t>-24,45; -10,59</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-55,51; -36,97</t>
+          <t>-55,08; -37,47</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-13,33; -2,36</t>
+          <t>-13,74; -3,14</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-21,32; -11,16</t>
+          <t>-20,87; -10,41</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-52,18; -38,94</t>
+          <t>-51,4; -39,13</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P19C03-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P19C03-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-21,49</t>
+          <t>-18,85</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-18,47</t>
+          <t>-16,71</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-20,17</t>
+          <t>-17,79</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-25,99; -9,09</t>
+          <t>-26,33; -8,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-18,01; 0,17</t>
+          <t>-17,88; 0,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-29,13; -12,61</t>
+          <t>-26,58; -10,73</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-24,05; -6,27</t>
+          <t>-25,19; -5,49</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-27,78; -9,82</t>
+          <t>-27,31; -9,73</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-26,57; -9,46</t>
+          <t>-24,72; -8,5</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-22,14; -9,85</t>
+          <t>-22,18; -9,72</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-20,07; -6,88</t>
+          <t>-20,03; -7,42</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-25,81; -13,67</t>
+          <t>-24,05; -12,03</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-59,74%</t>
+          <t>-52,4%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-45,03%</t>
+          <t>-40,73%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-52,3%</t>
+          <t>-46,14%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-62,74; -27,9</t>
+          <t>-62,77; -26,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-42,75; 1,44</t>
+          <t>-42,94; 3,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-72,44; -41,77</t>
+          <t>-65,42; -34,29</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-52,2; -17,35</t>
+          <t>-53,74; -14,5</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-59,25; -27,66</t>
+          <t>-59,53; -26,99</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-57,18; -27,16</t>
+          <t>-53,47; -23,93</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-52,75; -28,22</t>
+          <t>-53,53; -29,03</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-47,35; -19,84</t>
+          <t>-47,57; -20,45</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-61,2; -39,34</t>
+          <t>-56,22; -34,24</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-6,1</t>
+          <t>-6,6</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-8,97</t>
+          <t>-8,64</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-7,47</t>
+          <t>-7,6</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,76; 3,54</t>
+          <t>-10,34; 2,97</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,41; 5,91</t>
+          <t>-8,0; 6,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-12,91; 1,71</t>
+          <t>-13,29; 0,68</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,07; 6,03</t>
+          <t>-6,58; 6,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-9,86; 2,39</t>
+          <t>-10,37; 2,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-14,25; -3,21</t>
+          <t>-14,06; -3,29</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 2,98</t>
+          <t>-6,08; 2,86</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-7,32; 2,03</t>
+          <t>-7,24; 1,95</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-12,11; -3,06</t>
+          <t>-12,44; -3,14</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-18,12%</t>
+          <t>-19,62%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-29,05%</t>
+          <t>-27,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-23,18%</t>
+          <t>-23,58%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-26,46; 11,63</t>
+          <t>-27,96; 9,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-22,98; 19,53</t>
+          <t>-21,91; 20,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-34,69; 6,06</t>
+          <t>-36,33; 1,37</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-18,06; 21,35</t>
+          <t>-19,29; 23,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-29,92; 8,5</t>
+          <t>-30,88; 6,96</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-41,57; -11,1</t>
+          <t>-41,5; -11,7</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-17,25; 9,82</t>
+          <t>-17,64; 9,55</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-21,32; 6,84</t>
+          <t>-20,98; 6,66</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-35,29; -10,04</t>
+          <t>-35,37; -10,32</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-13,54</t>
+          <t>-13,35</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-15,46</t>
+          <t>-15,27</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-14,51</t>
+          <t>-14,34</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,77; 9,32</t>
+          <t>-6,72; 10,28</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-12,65; 3,73</t>
+          <t>-11,73; 4,4</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-21,11; -5,94</t>
+          <t>-20,88; -6,02</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-10,2; 5,1</t>
+          <t>-10,57; 3,8</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-12,26; 1,95</t>
+          <t>-13,25; 0,9</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-21,05; -9,19</t>
+          <t>-21,66; -9,56</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-6,58; 4,27</t>
+          <t>-6,43; 4,51</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-10,06; 0,95</t>
+          <t>-10,13; 0,49</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-19,52; -10,08</t>
+          <t>-19,22; -10,25</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-42,97%</t>
+          <t>-42,34%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-52,0%</t>
+          <t>-51,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-47,52%</t>
+          <t>-46,96%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-21,13; 34,71</t>
+          <t>-18,6; 39,14</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-35,56; 13,63</t>
+          <t>-32,17; 16,94</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-58,39; -22,2</t>
+          <t>-58,51; -22,38</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-30,06; 20,53</t>
+          <t>-30,69; 15,67</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-37,92; 6,69</t>
+          <t>-38,32; 3,83</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-63,58; -35,76</t>
+          <t>-63,44; -36,39</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-20,02; 15,32</t>
+          <t>-19,1; 16,4</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-29,61; 3,93</t>
+          <t>-30,48; 1,6</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-57,93; -36,18</t>
+          <t>-56,71; -36,28</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-12,35</t>
+          <t>-11,97</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-10,44</t>
+          <t>-12,86</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-11,16</t>
+          <t>-12,44</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,17; 10,01</t>
+          <t>-5,12; 9,79</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-20,33; -6,29</t>
+          <t>-19,77; -6,01</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-19,85; -3,34</t>
+          <t>-20,01; -3,62</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-14,17; 0,35</t>
+          <t>-13,53; 0,39</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-14,17; -0,54</t>
+          <t>-14,5; -0,64</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-20,38; 7,05</t>
+          <t>-19,02; -6,01</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-7,84; 2,42</t>
+          <t>-7,55; 3,05</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-15,51; -5,73</t>
+          <t>-15,44; -5,23</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-17,93; 0,23</t>
+          <t>-17,54; -6,88</t>
         </is>
       </c>
     </row>
@@ -1388,37 +1388,37 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
+          <t>-38,11%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>-21,48%</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>-24,15%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>-40,38%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>-7,71%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>-33,07%</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
           <t>-39,32%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-21,48%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-24,15%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>-32,78%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>-7,71%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>-33,07%</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>-35,28%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-14,85; 35,53</t>
+          <t>-14,96; 36,36</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-57,41; -22,88</t>
+          <t>-57,15; -22,12</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-57,65; -10,5</t>
+          <t>-56,45; -12,17</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-40,59; 1,22</t>
+          <t>-37,7; 2,2</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-41,2; -1,92</t>
+          <t>-41,25; -2,06</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-60,91; 27,03</t>
+          <t>-54,45; -20,86</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-23,11; 8,05</t>
+          <t>-22,85; 10,28</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-44,72; -19,41</t>
+          <t>-44,19; -17,95</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-54,34; 1,08</t>
+          <t>-50,73; -23,8</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-7,32</t>
+          <t>-7,82</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-5,25</t>
+          <t>-6,01</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-6,22</t>
+          <t>-6,87</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-7,33; 12,25</t>
+          <t>-6,59; 12,79</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-14,7; 5,63</t>
+          <t>-14,65; 6,88</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-16,38; 1,06</t>
+          <t>-17,69; 0,2</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-8,46; 10,85</t>
+          <t>-7,05; 12,55</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-12,56; 6,41</t>
+          <t>-13,4; 5,48</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-13,56; 2,93</t>
+          <t>-14,44; 0,88</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 9,24</t>
+          <t>-4,58; 9,41</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-11,75; 2,05</t>
+          <t>-11,12; 2,88</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-12,13; -0,7</t>
+          <t>-13,14; -1,73</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-25,55%</t>
+          <t>-27,28%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-18,8%</t>
+          <t>-21,53%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-21,99%</t>
+          <t>-24,29%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-22,55; 48,83</t>
+          <t>-19,53; 56,41</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-45,0; 23,37</t>
+          <t>-44,29; 27,38</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-47,91; 4,57</t>
+          <t>-49,93; 0,99</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-25,34; 46,57</t>
+          <t>-22,02; 56,84</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-38,43; 27,22</t>
+          <t>-42,28; 23,97</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-39,24; 14,15</t>
+          <t>-42,56; 3,81</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-14,33; 39,03</t>
+          <t>-14,28; 37,96</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-36,96; 8,47</t>
+          <t>-36,57; 11,03</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-37,44; -3,05</t>
+          <t>-39,85; -6,57</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-5,87</t>
+          <t>-5,51</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-9,73</t>
+          <t>-9,78</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-7,69</t>
+          <t>-7,6</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-11,34; 6,61</t>
+          <t>-11,44; 5,62</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-15,21; 1,83</t>
+          <t>-15,38; 2,38</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-14,22; 2,08</t>
+          <t>-13,81; 2,53</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-7,69; 8,64</t>
+          <t>-7,58; 8,99</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-12,35; 3,89</t>
+          <t>-12,4; 3,54</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-17,86; -3,23</t>
+          <t>-17,71; -3,58</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-6,7; 4,43</t>
+          <t>-6,96; 5,36</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-10,98; 0,5</t>
+          <t>-10,72; 0,9</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-12,66; -2,05</t>
+          <t>-13,28; -2,1</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-20,24%</t>
+          <t>-18,99%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-37,58%</t>
+          <t>-37,78%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-28,08%</t>
+          <t>-27,75%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-34,19; 28,28</t>
+          <t>-34,17; 23,49</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-45,15; 7,49</t>
+          <t>-46,3; 10,15</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-42,42; 8,28</t>
+          <t>-41,05; 10,29</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-24,52; 39,79</t>
+          <t>-26,03; 40,99</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-40,52; 18,99</t>
+          <t>-40,67; 18,05</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-56,88; -14,13</t>
+          <t>-56,49; -15,54</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-21,95; 17,93</t>
+          <t>-22,45; 22,76</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-36,26; 2,47</t>
+          <t>-35,28; 4,12</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-41,55; -7,98</t>
+          <t>-42,74; -8,85</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-10,06</t>
+          <t>-11,25</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-15,66</t>
+          <t>-10,31</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-13,4</t>
+          <t>-10,72</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-8,39; 2,45</t>
+          <t>-9,81; 2,17</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-4,89; 9,04</t>
+          <t>-4,82; 8,29</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-16,52; -3,95</t>
+          <t>-17,21; -4,99</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-8,7; 2,86</t>
+          <t>-8,86; 1,45</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 7,76</t>
+          <t>-4,08; 7,33</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-24,94; -8,97</t>
+          <t>-15,13; -5,39</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-7,4; 0,82</t>
+          <t>-7,65; 0,7</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 6,65</t>
+          <t>-2,36; 6,33</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-21,2; -8,73</t>
+          <t>-14,33; -6,72</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-30,18%</t>
+          <t>-33,75%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-50,17%</t>
+          <t>-33,03%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-41,61%</t>
+          <t>-33,29%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-23,0; 8,09</t>
+          <t>-27,07; 7,27</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-13,19; 30,27</t>
+          <t>-13,63; 26,75</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-44,97; -13,19</t>
+          <t>-48,18; -16,84</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-26,0; 9,78</t>
+          <t>-26,71; 5,41</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-12,03; 27,1</t>
+          <t>-12,05; 25,74</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-77,01; -29,27</t>
+          <t>-44,4; -19,08</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-21,68; 2,82</t>
+          <t>-22,14; 2,34</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-7,0; 22,33</t>
+          <t>-6,79; 21,11</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-62,85; -28,04</t>
+          <t>-41,73; -22,28</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-22,97</t>
+          <t>-20,48</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-23,07</t>
+          <t>-23,17</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-23,44</t>
+          <t>-21,94</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 6,67</t>
+          <t>-4,48; 6,59</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-9,95; 0,55</t>
+          <t>-9,78; 0,8</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-30,26; -18,16</t>
+          <t>-25,65; -16,44</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-7,49; 3,99</t>
+          <t>-7,14; 3,48</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-13,09; -2,34</t>
+          <t>-13,58; -3,0</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-27,72; -18,68</t>
+          <t>-27,41; -18,92</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 3,46</t>
+          <t>-4,06; 3,28</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-10,5; -2,94</t>
+          <t>-10,2; -2,48</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-28,61; -20,04</t>
+          <t>-25,17; -18,74</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-74,78%</t>
+          <t>-66,67%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-65,44%</t>
+          <t>-65,72%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-70,76%</t>
+          <t>-66,23%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-11,87; 23,84</t>
+          <t>-13,33; 23,5</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-29,29; 1,95</t>
+          <t>-29,2; 3,24</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-88,33; -62,7</t>
+          <t>-75,04; -57,5</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-19,17; 12,47</t>
+          <t>-19,04; 10,74</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-34,53; -7,09</t>
+          <t>-35,53; -8,95</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-71,91; -58,12</t>
+          <t>-71,81; -58,64</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-11,93; 11,18</t>
+          <t>-11,49; 10,57</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-29,46; -9,31</t>
+          <t>-29,09; -8,11</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-82,41; -63,87</t>
+          <t>-71,86; -60,68</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>-14,05</t>
+          <t>-12,87</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>-14,62</t>
+          <t>-13,74</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-14,34</t>
+          <t>-13,32</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 0,43</t>
+          <t>-4,62; 0,66</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-6,92; -1,84</t>
+          <t>-7,29; -1,81</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-18,41; -11,35</t>
+          <t>-15,4; -10,22</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-5,43; -0,57</t>
+          <t>-5,67; -0,78</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-8,11; -3,24</t>
+          <t>-8,22; -3,13</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-18,25; -11,76</t>
+          <t>-15,78; -11,66</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-4,53; -0,98</t>
+          <t>-4,29; -0,76</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-6,89; -3,27</t>
+          <t>-7,09; -3,47</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-16,68; -12,24</t>
+          <t>-15,0; -11,61</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>-43,91%</t>
+          <t>-40,24%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-45,59%</t>
+          <t>-42,86%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-44,78%</t>
+          <t>-41,6%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-13,73; 1,46</t>
+          <t>-14,0; 2,01</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-20,69; -5,48</t>
+          <t>-21,71; -5,84</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-57,45; -36,86</t>
+          <t>-45,86; -33,43</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-16,3; -1,89</t>
+          <t>-17,05; -2,31</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-24,45; -10,59</t>
+          <t>-24,94; -10,32</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-55,08; -37,47</t>
+          <t>-47,28; -38,05</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-13,74; -3,14</t>
+          <t>-12,87; -2,34</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-20,87; -10,41</t>
+          <t>-21,54; -11,17</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-51,4; -39,13</t>
+          <t>-45,33; -37,14</t>
         </is>
       </c>
     </row>
